--- a/Venta acumulada del mes.xlsx
+++ b/Venta acumulada del mes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mystic\Métricas\DashboardVentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF560DA0-561A-47B8-912A-3958C6DEC343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573ABEFF-43A9-4155-9839-633183DDFF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -843,7 +843,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P233"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -903,7 +902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1400558</v>
       </c>
@@ -953,7 +952,7 @@
         <v>217.11</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4">
         <v>1400555</v>
       </c>
@@ -1003,7 +1002,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1400554</v>
       </c>
@@ -1053,7 +1052,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="4">
         <v>1400553</v>
       </c>
@@ -1103,7 +1102,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1400552</v>
       </c>
@@ -1153,7 +1152,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
         <v>1400551</v>
       </c>
@@ -1203,7 +1202,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>1400550</v>
       </c>
@@ -1253,7 +1252,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
         <v>1400548</v>
       </c>
@@ -1303,7 +1302,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>1400546</v>
       </c>
@@ -1353,7 +1352,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4">
         <v>1400545</v>
       </c>
@@ -1403,7 +1402,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>1400544</v>
       </c>
@@ -1453,7 +1452,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>1400543</v>
       </c>
@@ -1503,7 +1502,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>1400542</v>
       </c>
@@ -1553,7 +1552,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>1400541</v>
       </c>
@@ -1603,7 +1602,7 @@
         <v>260.13</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>1400540</v>
       </c>
@@ -1653,7 +1652,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>1400539</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>1400538</v>
       </c>
@@ -1753,7 +1752,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>1400537</v>
       </c>
@@ -1803,7 +1802,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>1400536</v>
       </c>
@@ -1853,7 +1852,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>1400535</v>
       </c>
@@ -1903,7 +1902,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>1400534</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>1400533</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>158.74</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>1400521</v>
       </c>
@@ -2053,7 +2052,7 @@
         <v>206.77</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
         <v>1400520</v>
       </c>
@@ -2103,7 +2102,7 @@
         <v>184.85</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>1400519</v>
       </c>
@@ -2153,7 +2152,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
         <v>1400518</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>260.13</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>1400517</v>
       </c>
@@ -2403,7 +2402,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>1400489</v>
       </c>
@@ -2553,7 +2552,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
         <v>1399823</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>1399792</v>
       </c>
@@ -2653,7 +2652,7 @@
         <v>270.73</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
         <v>1399787</v>
       </c>
@@ -2703,7 +2702,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>1399786</v>
       </c>
@@ -2753,7 +2752,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
         <v>1399785</v>
       </c>
@@ -2803,7 +2802,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>1399784</v>
       </c>
@@ -2853,7 +2852,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
         <v>1399783</v>
       </c>
@@ -2903,7 +2902,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>1399782</v>
       </c>
@@ -2953,7 +2952,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
         <v>1399781</v>
       </c>
@@ -3003,7 +3002,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>1399780</v>
       </c>
@@ -3053,7 +3052,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
         <v>1399779</v>
       </c>
@@ -3103,7 +3102,7 @@
         <v>126.73</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>1399761</v>
       </c>
@@ -3153,7 +3152,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
         <v>1399760</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>1399759</v>
       </c>
@@ -3253,7 +3252,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
         <v>1399514</v>
       </c>
@@ -3303,7 +3302,7 @@
         <v>166.48</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>1399512</v>
       </c>
@@ -3353,7 +3352,7 @@
         <v>280.7</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
         <v>1399508</v>
       </c>
@@ -3403,7 +3402,7 @@
         <v>158.74</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>1399505</v>
       </c>
@@ -3503,7 +3502,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>1398881</v>
       </c>
@@ -3553,7 +3552,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
         <v>1398880</v>
       </c>
@@ -3603,7 +3602,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>1398879</v>
       </c>
@@ -3653,7 +3652,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
         <v>1398871</v>
       </c>
@@ -3703,7 +3702,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>1398870</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
         <v>1398869</v>
       </c>
@@ -3803,7 +3802,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>1398868</v>
       </c>
@@ -3853,7 +3852,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
         <v>1398867</v>
       </c>
@@ -3903,7 +3902,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>1398866</v>
       </c>
@@ -3953,7 +3952,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
         <v>1398865</v>
       </c>
@@ -4003,7 +4002,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>1398864</v>
       </c>
@@ -4053,7 +4052,7 @@
         <v>142.63999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="4">
         <v>1398829</v>
       </c>
@@ -4103,7 +4102,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>1398828</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="4">
         <v>1398827</v>
       </c>
@@ -4253,7 +4252,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="4">
         <v>1398446</v>
       </c>
@@ -4303,7 +4302,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>1398445</v>
       </c>
@@ -4353,7 +4352,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="4">
         <v>1398444</v>
       </c>
@@ -4403,7 +4402,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>1398443</v>
       </c>
@@ -4453,7 +4452,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="4">
         <v>1398442</v>
       </c>
@@ -4503,7 +4502,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>1398441</v>
       </c>
@@ -4553,7 +4552,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="4">
         <v>1398440</v>
       </c>
@@ -4603,7 +4602,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>1398439</v>
       </c>
@@ -4653,7 +4652,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="4">
         <v>1398438</v>
       </c>
@@ -4703,7 +4702,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>1398437</v>
       </c>
@@ -4753,7 +4752,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="4">
         <v>1398436</v>
       </c>
@@ -4803,7 +4802,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>1398435</v>
       </c>
@@ -4853,7 +4852,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="4">
         <v>1398434</v>
       </c>
@@ -4903,7 +4902,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>1398433</v>
       </c>
@@ -4953,7 +4952,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="4">
         <v>1398432</v>
       </c>
@@ -5003,7 +5002,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>1398431</v>
       </c>
@@ -5053,7 +5052,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="4">
         <v>1398430</v>
       </c>
@@ -5103,7 +5102,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>1398429</v>
       </c>
@@ -5153,7 +5152,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="4">
         <v>1398428</v>
       </c>
@@ -5203,7 +5202,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>1398427</v>
       </c>
@@ -5253,7 +5252,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="4">
         <v>1398426</v>
       </c>
@@ -5303,7 +5302,7 @@
         <v>165.76</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>1398425</v>
       </c>
@@ -5553,7 +5552,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="4">
         <v>1398414</v>
       </c>
@@ -5603,7 +5602,7 @@
         <v>594.25</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>1398413</v>
       </c>
@@ -5653,7 +5652,7 @@
         <v>162.74</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="4">
         <v>1398081</v>
       </c>
@@ -5703,7 +5702,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>1398080</v>
       </c>
@@ -5753,7 +5752,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="4">
         <v>1398079</v>
       </c>
@@ -5803,7 +5802,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>1398078</v>
       </c>
@@ -6003,7 +6002,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>1397198</v>
       </c>
@@ -6053,7 +6052,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="4">
         <v>1397197</v>
       </c>
@@ -6253,7 +6252,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="4">
         <v>1397193</v>
       </c>
@@ -6303,7 +6302,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>1397192</v>
       </c>
@@ -6353,7 +6352,7 @@
         <v>162.74</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="4">
         <v>1397191</v>
       </c>
@@ -6503,7 +6502,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>1396867</v>
       </c>
@@ -6553,7 +6552,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="4">
         <v>1396866</v>
       </c>
@@ -6603,7 +6602,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>1396865</v>
       </c>
@@ -6653,7 +6652,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="4">
         <v>1396843</v>
       </c>
@@ -6703,7 +6702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>1396842</v>
       </c>
@@ -6753,7 +6752,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="4">
         <v>1396841</v>
       </c>
@@ -6903,7 +6902,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>1396831</v>
       </c>
@@ -6953,7 +6952,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="4">
         <v>1396828</v>
       </c>
@@ -7003,7 +7002,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>1396827</v>
       </c>
@@ -7053,7 +7052,7 @@
         <v>162.74</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="4">
         <v>1396826</v>
       </c>
@@ -7103,7 +7102,7 @@
         <v>270.8</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>1396825</v>
       </c>
@@ -7153,7 +7152,7 @@
         <v>162.78</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="4">
         <v>1396817</v>
       </c>
@@ -7253,7 +7252,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="4">
         <v>1396792</v>
       </c>
@@ -7303,7 +7302,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>1396791</v>
       </c>
@@ -7353,7 +7352,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="4">
         <v>1396789</v>
       </c>
@@ -7503,7 +7502,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
         <v>1396419</v>
       </c>
@@ -7553,7 +7552,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="4">
         <v>1396418</v>
       </c>
@@ -7653,7 +7652,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="4">
         <v>1396341</v>
       </c>
@@ -7701,7 +7700,7 @@
         <v>234.46</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
         <v>1396338</v>
       </c>
@@ -7949,7 +7948,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="4">
         <v>1396325</v>
       </c>
@@ -7999,7 +7998,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
         <v>1396324</v>
       </c>
@@ -8049,7 +8048,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="4">
         <v>1396323</v>
       </c>
@@ -8149,7 +8148,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="4">
         <v>1396316</v>
       </c>
@@ -8197,7 +8196,7 @@
         <v>358.53</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
         <v>1396304</v>
       </c>
@@ -8247,7 +8246,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="4">
         <v>1396303</v>
       </c>
@@ -8297,7 +8296,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
         <v>1396301</v>
       </c>
@@ -8347,7 +8346,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="4">
         <v>1396300</v>
       </c>
@@ -8397,7 +8396,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="2">
         <v>1396298</v>
       </c>
@@ -8447,7 +8446,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="153" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="4">
         <v>1396297</v>
       </c>
@@ -8497,7 +8496,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="154" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
         <v>1396296</v>
       </c>
@@ -8547,7 +8546,7 @@
         <v>393.45</v>
       </c>
     </row>
-    <row r="155" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="4">
         <v>1396295</v>
       </c>
@@ -8597,7 +8596,7 @@
         <v>287.07</v>
       </c>
     </row>
-    <row r="156" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
         <v>1396294</v>
       </c>
@@ -8647,7 +8646,7 @@
         <v>87.41</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="4">
         <v>1396293</v>
       </c>
@@ -8697,7 +8696,7 @@
         <v>208.1</v>
       </c>
     </row>
-    <row r="158" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
         <v>1396291</v>
       </c>
@@ -8747,7 +8746,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="159" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A159" s="4">
         <v>1396270</v>
       </c>
@@ -8797,7 +8796,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="160" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
         <v>1396269</v>
       </c>
@@ -8847,7 +8846,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="161" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A161" s="4">
         <v>1396268</v>
       </c>
@@ -8897,7 +8896,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
         <v>1395850</v>
       </c>
@@ -8947,7 +8946,7 @@
         <v>594.25</v>
       </c>
     </row>
-    <row r="163" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A163" s="4">
         <v>1395845</v>
       </c>
@@ -8997,7 +8996,7 @@
         <v>557.08000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
         <v>1395840</v>
       </c>
@@ -9047,7 +9046,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A165" s="4">
         <v>1395839</v>
       </c>
@@ -9097,7 +9096,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="166" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
         <v>1395826</v>
       </c>
@@ -9147,7 +9146,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A167" s="4">
         <v>1395825</v>
       </c>
@@ -9197,7 +9196,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="168" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
         <v>1395786</v>
       </c>
@@ -9297,7 +9296,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="170" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
         <v>1395438</v>
       </c>
@@ -9347,7 +9346,7 @@
         <v>665.66</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="4">
         <v>1395436</v>
       </c>
@@ -9397,7 +9396,7 @@
         <v>282.76</v>
       </c>
     </row>
-    <row r="172" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
         <v>1395434</v>
       </c>
@@ -9447,7 +9446,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="173" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="4">
         <v>1395433</v>
       </c>
@@ -9497,7 +9496,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="174" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
         <v>1395432</v>
       </c>
@@ -9547,7 +9546,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="175" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="4">
         <v>1395422</v>
       </c>
@@ -9597,7 +9596,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="176" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
         <v>1395421</v>
       </c>
@@ -9647,7 +9646,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="4">
         <v>1395420</v>
       </c>
@@ -9697,7 +9696,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
         <v>1395419</v>
       </c>
@@ -9747,7 +9746,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="4">
         <v>1395418</v>
       </c>
@@ -9797,7 +9796,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="180" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="2">
         <v>1395417</v>
       </c>
@@ -9847,7 +9846,7 @@
         <v>318.97000000000003</v>
       </c>
     </row>
-    <row r="181" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="4">
         <v>1395416</v>
       </c>
@@ -9897,7 +9896,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="182" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="2">
         <v>1395415</v>
       </c>
@@ -9947,7 +9946,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="183" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="4">
         <v>1395414</v>
       </c>
@@ -9997,7 +9996,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="184" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="2">
         <v>1395413</v>
       </c>
@@ -10047,7 +10046,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="185" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="4">
         <v>1395412</v>
       </c>
@@ -10147,7 +10146,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="187" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A187" s="4">
         <v>1395410</v>
       </c>
@@ -10247,7 +10246,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="189" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A189" s="4">
         <v>1394175</v>
       </c>
@@ -10347,7 +10346,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="191" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A191" s="4">
         <v>1393801</v>
       </c>
@@ -10397,7 +10396,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="192" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
         <v>1393764</v>
       </c>
@@ -10447,7 +10446,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A193" s="4">
         <v>1393759</v>
       </c>
@@ -10497,7 +10496,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="194" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
         <v>1393746</v>
       </c>
@@ -10547,7 +10546,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="195" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A195" s="4">
         <v>1393739</v>
       </c>
@@ -10597,7 +10596,7 @@
         <v>234.46</v>
       </c>
     </row>
-    <row r="196" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
         <v>1393402</v>
       </c>
@@ -10697,7 +10696,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="198" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A198" s="2">
         <v>1393091</v>
       </c>
@@ -10747,7 +10746,7 @@
         <v>767.94</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A199" s="4">
         <v>1392686</v>
       </c>
@@ -10797,7 +10796,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="200" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A200" s="2">
         <v>1392682</v>
       </c>
@@ -10997,7 +10996,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A204" s="2">
         <v>1392102</v>
       </c>
@@ -11047,7 +11046,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A205" s="4">
         <v>1392101</v>
       </c>
@@ -11097,7 +11096,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="206" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A206" s="2">
         <v>1392100</v>
       </c>
@@ -11147,7 +11146,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A207" s="4">
         <v>1392099</v>
       </c>
@@ -11197,7 +11196,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="208" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A208" s="2">
         <v>1392098</v>
       </c>
@@ -11247,7 +11246,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="209" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A209" s="4">
         <v>1392063</v>
       </c>
@@ -11297,7 +11296,7 @@
         <v>22.07</v>
       </c>
     </row>
-    <row r="210" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A210" s="2">
         <v>1392059</v>
       </c>
@@ -11347,7 +11346,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A211" s="4">
         <v>1392058</v>
       </c>
@@ -11397,7 +11396,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="212" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A212" s="2">
         <v>1392029</v>
       </c>
@@ -11447,7 +11446,7 @@
         <v>286.8</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A213" s="4">
         <v>1391687</v>
       </c>
@@ -11547,7 +11546,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="215" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A215" s="4">
         <v>1390601</v>
       </c>
@@ -11597,7 +11596,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="216" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A216" s="2">
         <v>1390569</v>
       </c>
@@ -11747,7 +11746,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="219" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A219" s="4">
         <v>1390543</v>
       </c>
@@ -11797,7 +11796,7 @@
         <v>496.13</v>
       </c>
     </row>
-    <row r="220" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A220" s="2">
         <v>1390188</v>
       </c>
@@ -11847,7 +11846,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="221" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A221" s="4">
         <v>1390185</v>
       </c>
@@ -11897,7 +11896,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="222" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A222" s="2">
         <v>1390180</v>
       </c>
@@ -11947,7 +11946,7 @@
         <v>660.37</v>
       </c>
     </row>
-    <row r="223" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A223" s="4">
         <v>1390015</v>
       </c>
@@ -11997,7 +11996,7 @@
         <v>282.76</v>
       </c>
     </row>
-    <row r="224" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A224" s="2">
         <v>1390014</v>
       </c>
@@ -12047,7 +12046,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="225" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A225" s="4">
         <v>1390013</v>
       </c>
@@ -12097,7 +12096,7 @@
         <v>687.07</v>
       </c>
     </row>
-    <row r="226" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A226" s="2">
         <v>1390011</v>
       </c>
@@ -12147,7 +12146,7 @@
         <v>271.38</v>
       </c>
     </row>
-    <row r="227" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A227" s="4">
         <v>1390010</v>
       </c>
@@ -12197,7 +12196,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="228" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A228" s="2">
         <v>1390009</v>
       </c>
@@ -12247,7 +12246,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="229" spans="1:16" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A229" s="4">
         <v>1390005</v>
       </c>
@@ -12498,13 +12497,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P233" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="Juan Andrés Bastidas Pernías"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P233" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>